--- a/data/sample/synthetic_sales_order.xlsx
+++ b/data/sample/synthetic_sales_order.xlsx
@@ -489,52 +489,50 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46167</v>
+        <v>46140</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>83509687.39</v>
+        <v>94302476.13</v>
       </c>
       <c r="H2" t="n">
-        <v>73543162.97</v>
+        <v>64975570.47</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>46186</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46099</v>
+        <v>46051</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -542,18 +540,18 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>111396758.89</v>
+        <v>47439331</v>
       </c>
       <c r="H3" t="n">
-        <v>70077388.90000001</v>
+        <v>36777496.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Đã xuất hoá đơn</t>
+          <t>Đã thanh toán</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46111</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="4">
@@ -561,27 +559,27 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46235</v>
+        <v>45932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>333658634.37</v>
+        <v>428644421.77</v>
       </c>
       <c r="H4" t="n">
-        <v>264876216.63</v>
+        <v>265998039.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -595,69 +593,71 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>14</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9</v>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>46018</v>
+        <v>45952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>111963234.63</v>
+        <v>471966141.07</v>
       </c>
       <c r="H5" t="n">
-        <v>85191227.09</v>
+        <v>363839936.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Đã thanh toán</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45972</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46018</v>
+        <v>46105</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang vận chuyển</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>439753257.95</v>
+        <v>335539118.95</v>
       </c>
       <c r="H6" t="n">
-        <v>273797179.85</v>
+        <v>258220194.58</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
+          <t>Đã xuất hoá đơn</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46022</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="7">
@@ -665,61 +665,63 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45938</v>
+        <v>46026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>464656151.84</v>
+        <v>209977206.46</v>
       </c>
       <c r="H7" t="n">
-        <v>397099199.31</v>
+        <v>168298214.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Đã xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>46041</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46096</v>
+        <v>46125</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>453172575.45</v>
+        <v>318156442.64</v>
       </c>
       <c r="H8" t="n">
-        <v>294286253.77</v>
+        <v>244629882.24</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -733,71 +735,69 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46037</v>
+        <v>46150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Đang vận chuyển</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>223043593.28</v>
+        <v>147296199.08</v>
       </c>
       <c r="H9" t="n">
-        <v>197883225.93</v>
+        <v>129617387.19</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>46053</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45920</v>
+        <v>45971</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>298006539.59</v>
+        <v>230328595.04</v>
       </c>
       <c r="H10" t="n">
-        <v>227277238.48</v>
+        <v>175732746.04</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
+          <t>Đã xuất hoá đơn</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>45931</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="11">
@@ -805,137 +805,143 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46148</v>
+        <v>46232</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Đang vận chuyển</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>461305822.8</v>
+        <v>412209984.86</v>
       </c>
       <c r="H11" t="n">
-        <v>350286967.33</v>
+        <v>284348064.19</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Đã thanh toán</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>46236</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45926</v>
+        <v>45945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Đang vận chuyển</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>305616851.1</v>
+        <v>376360008.31</v>
       </c>
       <c r="H12" t="n">
-        <v>245277011</v>
+        <v>243367317.97</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>Đã xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>45965</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>19</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46017</v>
+        <v>46242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>297881147.6</v>
+        <v>324434220.26</v>
       </c>
       <c r="H13" t="n">
-        <v>182280176.15</v>
+        <v>220354155.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Đã xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>46251</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46158</v>
+        <v>46107</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Đang vận chuyển</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>171857526.07</v>
+        <v>418087082.9</v>
       </c>
       <c r="H14" t="n">
-        <v>116558879.84</v>
+        <v>256381881.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
+          <t>Đã xuất hoá đơn</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46169</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="15">
@@ -943,27 +949,27 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46234</v>
+        <v>46117</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>329840378.64</v>
+        <v>284806602.14</v>
       </c>
       <c r="H15" t="n">
-        <v>243147565.03</v>
+        <v>207426378.74</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -977,27 +983,27 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45942</v>
+        <v>46244</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>55165146.13</v>
+        <v>453885714.35</v>
       </c>
       <c r="H16" t="n">
-        <v>36626694.31</v>
+        <v>346622120.06</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1005,7 +1011,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>45947</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="17">
@@ -1013,63 +1019,61 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46016</v>
+        <v>45956</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>197373002.59</v>
+        <v>40077851.92</v>
       </c>
       <c r="H17" t="n">
-        <v>127764291.34</v>
+        <v>28431045.98</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>46026</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46232</v>
+        <v>46018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>412209984.86</v>
+        <v>340128037.11</v>
       </c>
       <c r="H18" t="n">
-        <v>284348064.19</v>
+        <v>240165628.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1077,7 +1081,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46236</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="19">
@@ -1085,71 +1089,69 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45945</v>
+        <v>46012</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>376360008.31</v>
+        <v>435010734.19</v>
       </c>
       <c r="H19" t="n">
-        <v>243367317.97</v>
+        <v>388404471.45</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Đã xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>45965</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46242</v>
+        <v>46061</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>324434220.26</v>
+        <v>395545518.15</v>
       </c>
       <c r="H20" t="n">
-        <v>220354155.54</v>
+        <v>286182700.23</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Đã xuất hoá đơn</t>
+          <t>Đã thanh toán</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46251</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="21">
@@ -1157,16 +1159,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46032</v>
+        <v>46250</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1174,33 +1176,35 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>41161645.66</v>
+        <v>71885900.67</v>
       </c>
       <c r="H21" t="n">
-        <v>28815908.21</v>
+        <v>61940488.82</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Đã xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>46258</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46173</v>
+        <v>46047</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1208,10 +1212,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>358720374.44</v>
+        <v>413857462.87</v>
       </c>
       <c r="H22" t="n">
-        <v>275594840.83</v>
+        <v>356495540.01</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1225,35 +1229,35 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
         <v>14</v>
       </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
       <c r="E23" s="2" t="n">
-        <v>46170</v>
+        <v>46059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37293506.27</v>
+        <v>153729469.29</v>
       </c>
       <c r="H23" t="n">
-        <v>26506911.35</v>
+        <v>95439286.31</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
+          <t>Đã xuất hoá đơn</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46175</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="24">
@@ -1261,27 +1265,27 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46077</v>
+        <v>46238</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Đang vận chuyển</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>451511114.6</v>
+        <v>490951849.86</v>
       </c>
       <c r="H24" t="n">
-        <v>378744089.53</v>
+        <v>373547941.65</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1295,156 +1299,156 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Đã giao</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>69340938.40000001</v>
+        <v>482016471.57</v>
       </c>
       <c r="H25" t="n">
-        <v>57832760.72</v>
+        <v>327597630.76</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Đã xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>46252</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45974</v>
+        <v>46051</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>488578895.81</v>
+        <v>229469064.26</v>
       </c>
       <c r="H26" t="n">
-        <v>411985122.99</v>
+        <v>205436942.36</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Đã xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>45975</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46101</v>
+        <v>46021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>405072866.69</v>
+        <v>41305536.18</v>
       </c>
       <c r="H27" t="n">
-        <v>348046387.91</v>
+        <v>30186798.55</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Đã thanh toán</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>46039</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>46086</v>
+        <v>46111</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>438640055.79</v>
+        <v>53587429.34</v>
       </c>
       <c r="H28" t="n">
-        <v>376168050.97</v>
+        <v>42830894.61</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Đã xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>46131</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46007</v>
+        <v>46044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1452,10 +1456,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>127003302.66</v>
+        <v>263418801.94</v>
       </c>
       <c r="H29" t="n">
-        <v>101349899.82</v>
+        <v>210752920.11</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1463,7 +1467,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46018</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="30">
@@ -1471,35 +1475,35 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>46070</v>
+        <v>45956</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>327911234.53</v>
+        <v>112083244.64</v>
       </c>
       <c r="H30" t="n">
-        <v>236064450.45</v>
+        <v>89608181.31999999</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
+          <t>Đã xuất hoá đơn</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46081</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="31">
@@ -1507,95 +1511,99 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="n">
-        <v>5</v>
-      </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45982</v>
+        <v>46098</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>298683072.19</v>
+        <v>283009862.31</v>
       </c>
       <c r="H31" t="n">
-        <v>267340815.34</v>
+        <v>169840382.87</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Đã xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>46105</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>46051</v>
+        <v>46226</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Đã giao</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>229469064.26</v>
+        <v>174679630.27</v>
       </c>
       <c r="H32" t="n">
-        <v>205436942.36</v>
+        <v>127959083.59</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>Đã thanh toán</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>46233</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45913</v>
+        <v>45977</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Đang vận chuyển</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>360216936.24</v>
+        <v>336248357.6</v>
       </c>
       <c r="H33" t="n">
-        <v>216312929.86</v>
+        <v>230375828.34</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1603,7 +1611,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>45920</v>
+        <v>45997</v>
       </c>
     </row>
     <row r="34">
@@ -1611,52 +1619,50 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46210</v>
+        <v>46011</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Mới tạo</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>170679509.63</v>
+        <v>342941921.87</v>
       </c>
       <c r="H34" t="n">
-        <v>145829355.4</v>
+        <v>228876763.64</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>46220</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>46058</v>
+        <v>46016</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1664,10 +1670,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>213152185.79</v>
+        <v>492289290.94</v>
       </c>
       <c r="H35" t="n">
-        <v>146797177.27</v>
+        <v>385650663.79</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1681,35 +1687,35 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46237</v>
+        <v>46213</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>379104588.88</v>
+        <v>296322031.72</v>
       </c>
       <c r="H36" t="n">
-        <v>247255122.65</v>
+        <v>241651735.38</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
+          <t>Đã xuất hoá đơn</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46247</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="37">
@@ -1717,122 +1723,120 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46046</v>
+        <v>46226</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Đã giao</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>157718584.1</v>
+        <v>350058758.28</v>
       </c>
       <c r="H37" t="n">
-        <v>114971555.56</v>
+        <v>303780272.07</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>46066</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>46117</v>
+        <v>46247</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Đã giao</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>344301071.93</v>
+        <v>268619720.21</v>
       </c>
       <c r="H38" t="n">
-        <v>259379969.68</v>
+        <v>165218726.7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>46123</v>
-      </c>
+          <t>Chưa xuất hoá đơn</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>46230</v>
+        <v>46128</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Đang xử lý</t>
+          <t>Huỷ</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>323811610.77</v>
+        <v>340437311.64</v>
       </c>
       <c r="H39" t="n">
-        <v>226848321.13</v>
+        <v>305157022.26</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chưa xuất hoá đơn</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Đã thanh toán</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>46139</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45966</v>
+        <v>46149</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1840,10 +1844,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>31724186.11</v>
+        <v>224835563.29</v>
       </c>
       <c r="H40" t="n">
-        <v>21364740.8</v>
+        <v>196069296.22</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1851,7 +1855,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>45986</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="41">
@@ -1859,27 +1863,27 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46213</v>
+        <v>46023</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mới tạo</t>
+          <t>Đang xử lý</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>296322031.72</v>
+        <v>380852857.52</v>
       </c>
       <c r="H41" t="n">
-        <v>241651735.38</v>
+        <v>324470968.74</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1887,7 +1891,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46229</v>
+        <v>46040</v>
       </c>
     </row>
   </sheetData>
